--- a/06.03.xlsx
+++ b/06.03.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>姓名</t>
   </si>
@@ -57,6 +57,12 @@
   </si>
   <si>
     <t>学历</t>
+  </si>
+  <si>
+    <t>培训日期</t>
+  </si>
+  <si>
+    <t>考试成绩</t>
   </si>
   <si>
     <t>有效期限</t>
@@ -1036,7 +1042,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="4" max="4" width="4.90909090909091" customWidth="1"/>
@@ -1046,7 +1052,7 @@
     <col min="8" max="8" width="20.7272727272727" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1094,6 +1100,12 @@
       </c>
       <c r="P1" t="s">
         <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
